--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,11 @@
           <t>76.307.580-k</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>96.827.350-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>77.714.387-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1185,7 +1209,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>557639-793-CM25</t>
+          <t>730566-292-SE25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,47 +1224,51 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>96.771.610-3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1108739.21</v>
+        <v>31755.31</v>
       </c>
     </row>
     <row r="14">
@@ -1307,7 +1335,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1177296-247-CM25</t>
+          <t>557639-793-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,37 +1350,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Toledo y Badilla Profesionales Ltda.</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.084.696-1</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1390,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>31008.36</v>
+        <v>1108739.21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1434-75-CM25</t>
+          <t>1177296-247-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,17 +1416,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1436,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>KLEINROCK SPA</t>
+          <t>Toledo y Badilla Profesionales Ltda.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.146.212-K</t>
+          <t>76.084.696-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1451,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>29246.76</v>
+        <v>31008.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>761-340-CM25</t>
+          <t>1434-75-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1472,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,28 +1497,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+          <t>KLEINROCK SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.011.651-3</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>77.146.212-K</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>123735.3</v>
+        <v>29246.76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1592-105-CM25</t>
+          <t>761-340-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1515,12 +1547,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.503.000-7</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVISION SOCIAL</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1562,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.011.651-3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1577,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6840.39</v>
+        <v>123735.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1057049-13789-CM25</t>
+          <t>1592-105-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1598,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1608,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.503.000-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SUBSECRETARIA DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1623,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1638,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>22135.94</v>
+        <v>6840.39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>188-627-CM25</t>
+          <t>1591-200-SE25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1659,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,28 +1684,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>77.077.350-4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7142.56</v>
+        <v>7595.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1056854-62-CM25</t>
+          <t>1057049-13789-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1724,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1734,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,28 +1749,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>LUUK SPA</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.363.384-3</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9639.24</v>
+        <v>22135.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1725-5116-CM25</t>
+          <t>188-627-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,37 +1789,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1829,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6674.1</v>
+        <v>7142.56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2268-132-CM25</t>
+          <t>730566-303-SE25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1850,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,28 +1875,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>77.842.230-1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>819024.72</v>
+        <v>32162.45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5251-1130-CM25</t>
+          <t>1725-5116-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,12 +1925,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,28 +1940,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>25627.42</v>
+        <v>6674.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>587-375-CM25</t>
+          <t>2268-132-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,22 +1980,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,28 +2005,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>KUANTUM SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.553.335-K</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>32030.67</v>
+        <v>819024.72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1233600-547-CM25</t>
+          <t>5251-1130-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +2045,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,43 +2055,47 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.931.100-K</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE RENCA</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>28470.87</v>
+        <v>25627.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1562-276-CM25</t>
+          <t>1056854-62-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2110,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,43 +2120,47 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>LUUK SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.363.384-3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>24140.41</v>
+        <v>9639.24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1725-5144-CM25</t>
+          <t>1592-108-SE25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,43 +2185,47 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.503.000-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SUBSECRETARIA DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>CODER HUB SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>76.734.221-7</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>20039.98</v>
+        <v>413754.26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057421-1040-CM25</t>
+          <t>1233600-547-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2240,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,17 +2250,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.607.306-0</t>
+          <t>70.931.100-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE LAJA</t>
+          <t>CORP MUNICIPAL DE RENCA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2216,13 +2280,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>8226.469999999999</v>
+        <v>28470.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1098710-271-CM25</t>
+          <t>587-375-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,22 +2301,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>62.000.740-4</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2326,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>KUANTUM SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.553.335-K</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2341,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>35835.81</v>
+        <v>32030.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1529-270-CM25</t>
+          <t>1562-276-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2362,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2372,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,28 +2387,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>43420.29</v>
+        <v>24140.41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1057421-1041-CM25</t>
+          <t>1078113-24-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,27 +2437,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.607.306-0</t>
+          <t>60.510.000-7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE LAJA</t>
+          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2467,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>13876.46</v>
+        <v>35545.48</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1147293-129-CM25</t>
+          <t>1078113-26-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,12 +2498,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>70.930.000-8</t>
+          <t>60.510.000-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fundación para la Innovación Agraria</t>
+          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,28 +2513,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ARKAVIA NETWORKS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.083.362-2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>21133.65</v>
+        <v>24070.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1078113-26-CM25</t>
+          <t>1147293-129-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,12 +2563,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>70.930.000-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>Fundación para la Innovación Agraria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2578,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>ARKAVIA NETWORKS SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.083.362-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2593,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>24070.64</v>
+        <v>21133.65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1078113-24-CM25</t>
+          <t>621923-28-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,12 +2624,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>53.314.945-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2654,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>35545.48</v>
+        <v>25917.41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>621923-28-CM25</t>
+          <t>1529-270-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,27 +2685,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>53.314.945-6</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2715,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>25917.41</v>
+        <v>43420.29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1111089-263-CM25</t>
+          <t>1098710-271-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2736,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2746,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>62.000.740-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,28 +2761,32 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Smartnodus SpA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.461.797-5</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>10711.95</v>
+        <v>35835.81</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>875-90-CM25</t>
+          <t>1057421-1040-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2801,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,27 +2811,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.720.000-9</t>
+          <t>61.607.306-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE LAJA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2841,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>7307.07</v>
+        <v>8226.469999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3328-2166-CM25</t>
+          <t>1057421-1041-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2862,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,27 +2872,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.607.306-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE LAJA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>LIVISTER CHILE SPA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.622.841-9</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2902,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7564.89</v>
+        <v>13876.46</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>730566-333-CM25</t>
+          <t>1725-5144-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2923,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,27 +2933,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>VISIION LTDA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.436.870-1</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2963,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>49976.79</v>
+        <v>20039.98</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1588-148-CM25</t>
+          <t>1111089-263-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2984,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +3009,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>Smartnodus SpA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.461.797-5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +3024,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>17461.49</v>
+        <v>10711.95</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3553-378-CM25</t>
+          <t>875-90-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +3045,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +3055,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>60.720.000-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,28 +3070,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>77.077.350-4</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>18190.68</v>
+        <v>7307.07</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>761-328-CM25</t>
+          <t>730566-338-SE25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3110,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3120,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,28 +3135,32 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.093.443-7</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>76.504.980-6</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1601122.18</v>
+        <v>15430.36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1876-142-CM25</t>
+          <t>3328-2166-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3175,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3185,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,28 +3200,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>GLOBAL INNOVATION GROUP SPA</t>
+          <t>LIVISTER CHILE SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.423.763-3</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>77.622.841-9</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>76014.2</v>
+        <v>7564.89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1016-49-CM25</t>
+          <t>730566-333-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,22 +3240,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3265,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>VISIION LTDA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>77.436.870-1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3280,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>12979.59</v>
+        <v>49976.79</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>757-415-CM25</t>
+          <t>1588-148-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3301,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3311,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3326,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.444.489-2</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,67 +3341,644 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>39018.88</v>
+        <v>17461.49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>709603-145-SE25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>61.980.220-9</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>25665.17</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>709603-146-SE25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>61.980.220-9</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>XMS Business Solutions S.A.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.249.938-k</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>26066.18</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3553-378-CM25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>61.402.000-8</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>18190.68</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>761-328-CM25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>60.515.000-4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.093.443-7</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>1601122.18</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1876-142-CM25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.941.900-6</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DEFENSORIA PENAL PUBLICA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>GLOBAL INNOVATION GROUP SPA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76.423.763-3</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>76014.2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>593951-476-SE25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>INGENIERIA SD</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.300.658-1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>50528.49</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1016-49-CM25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>12979.59</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1057547-26417-SE25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>45570.52</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>757-415-CM25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>61.601.000-k</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>76.444.489-2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>39018.88</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>4907-11-CM25</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>jul-2025</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>60.905.000-4</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
         <is>
           <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>76.198.095-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="n">
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
         <v>58866.46</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/jul-2025.xlsx
@@ -2956,7 +2956,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
